--- a/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
+++ b/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B88465D-AE5D-465C-9380-D16C33D0C4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AEA0491-0BBE-446E-9224-67E4D680E8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A79FFA26-B743-4EEB-A00B-8C196410CA24}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1512071C-8381-4D3B-BA6B-8302DC459B45}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B5BE24-6D30-463E-9E78-9711349DCFA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A69765-B72F-41CC-89CC-4DE00004D365}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -895,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>9.2294400000000026E-2</v>
+        <v>8.6756736000000029E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -951,7 +951,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>9.2294400000000026E-2</v>
+        <v>8.6756736000000029E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -1007,19 +1007,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.12668399999999999</v>
+        <v>8.9385728000000025E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -1063,19 +1063,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.12668399999999999</v>
+        <v>8.9385728000000025E-2</v>
       </c>
       <c r="F15">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G15">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H15">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I15">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -1119,7 +1119,7 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>0.28982625000000001</v>
+        <v>0.27533493750000004</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -1175,7 +1175,7 @@
         <v>22</v>
       </c>
       <c r="E17">
-        <v>0.24150000000000002</v>
+        <v>0.22942499999999999</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>0.24150000000000002</v>
+        <v>0.22942499999999999</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.24150000000000002</v>
+        <v>0.22942499999999999</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D434E9-86E2-4571-9909-DBB2BD05734C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4E6D1A-F526-4B26-B12B-A425F51BF8C4}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1895,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570F00A2-438D-44AC-A742-C05A1858B2FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D99CE4-2C84-432E-8949-12005D422FD0}">
   <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1980,7 +1980,7 @@
         <v>0.05</v>
       </c>
       <c r="G11">
-        <v>0.30360000000000004</v>
+        <v>0.28538400000000003</v>
       </c>
       <c r="H11">
         <v>2160</v>
@@ -2033,7 +2033,7 @@
         <v>0.05</v>
       </c>
       <c r="G12">
-        <v>0.30360000000000004</v>
+        <v>0.28538400000000003</v>
       </c>
       <c r="H12">
         <v>2160</v>
@@ -2086,7 +2086,7 @@
         <v>0.15</v>
       </c>
       <c r="G13">
-        <v>0.31280000000000002</v>
+        <v>0.29403200000000002</v>
       </c>
       <c r="H13">
         <v>1840</v>
@@ -2139,7 +2139,7 @@
         <v>0.15</v>
       </c>
       <c r="G14">
-        <v>0.31280000000000002</v>
+        <v>0.29403200000000002</v>
       </c>
       <c r="H14">
         <v>1840</v>
@@ -2192,7 +2192,7 @@
         <v>4.0000000000000036E-3</v>
       </c>
       <c r="G15">
-        <v>0.33123000000000002</v>
+        <v>0.31466850000000002</v>
       </c>
       <c r="N15" t="s">
         <v>51</v>
@@ -2233,7 +2233,7 @@
         <v>0.06</v>
       </c>
       <c r="G16">
-        <v>0.27600000000000002</v>
+        <v>0.26219999999999999</v>
       </c>
       <c r="H16">
         <v>1104</v>
@@ -2286,7 +2286,7 @@
         <v>0.06</v>
       </c>
       <c r="G17">
-        <v>0.27600000000000002</v>
+        <v>0.26219999999999999</v>
       </c>
       <c r="H17">
         <v>1104</v>
@@ -2339,7 +2339,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="G18">
-        <v>0.27600000000000002</v>
+        <v>0.26219999999999999</v>
       </c>
       <c r="H18">
         <v>1104</v>
@@ -2937,7 +2937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619650F0-1274-4CDB-B992-FB264E45F1B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3A4F7B-F234-48F5-957D-BDE7D2AF5183}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
+++ b/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AEA0491-0BBE-446E-9224-67E4D680E8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F38C79B-D497-4A16-A630-222804E28812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1512071C-8381-4D3B-BA6B-8302DC459B45}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FE76C27A-99DE-497A-B448-B53129901C0C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A69765-B72F-41CC-89CC-4DE00004D365}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE38C56D-D601-4330-BD0D-3A2929E76F96}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1119,7 +1119,7 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>0.27533493750000004</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -1175,7 +1175,7 @@
         <v>22</v>
       </c>
       <c r="E17">
-        <v>0.22942499999999999</v>
+        <v>0.24150000000000002</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>0.22942499999999999</v>
+        <v>0.24150000000000002</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.22942499999999999</v>
+        <v>0.24150000000000002</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4E6D1A-F526-4B26-B12B-A425F51BF8C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6A6F98-0948-4710-B075-D759353EF6D2}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1895,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D99CE4-2C84-432E-8949-12005D422FD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9BC4DF-B57B-4A70-8DE0-EBA46A9AA696}">
   <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2192,7 +2192,7 @@
         <v>4.0000000000000036E-3</v>
       </c>
       <c r="G15">
-        <v>0.31466850000000002</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N15" t="s">
         <v>51</v>
@@ -2233,7 +2233,7 @@
         <v>0.06</v>
       </c>
       <c r="G16">
-        <v>0.26219999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="H16">
         <v>1104</v>
@@ -2286,7 +2286,7 @@
         <v>0.06</v>
       </c>
       <c r="G17">
-        <v>0.26219999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="H17">
         <v>1104</v>
@@ -2339,7 +2339,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="G18">
-        <v>0.26219999999999999</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="H18">
         <v>1104</v>
@@ -2937,7 +2937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3A4F7B-F234-48F5-957D-BDE7D2AF5183}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA059683-4B18-4307-A825-FA8BBF3D9E8C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
+++ b/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F38C79B-D497-4A16-A630-222804E28812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA840356-C940-47F2-8659-BF16091C7B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FE76C27A-99DE-497A-B448-B53129901C0C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FADA588E-3174-45EF-A5AF-AE4C341BDD0C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE38C56D-D601-4330-BD0D-3A2929E76F96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C586DB-D571-4E0C-8454-C8B6F2FA60B6}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6A6F98-0948-4710-B075-D759353EF6D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB46C81-9F11-459F-96ED-5AA54ADC317F}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1895,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9BC4DF-B57B-4A70-8DE0-EBA46A9AA696}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E918A590-98E8-44F5-B283-965AE8712BE7}">
   <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2937,7 +2937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA059683-4B18-4307-A825-FA8BBF3D9E8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA764029-DD5A-442B-962B-E7D65027B404}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
+++ b/VerveStacks_TJK_grids/vt_vervestacks_TJK_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA840356-C940-47F2-8659-BF16091C7B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3122F6AA-2886-4EB7-BED0-76B39AE9E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FADA588E-3174-45EF-A5AF-AE4C341BDD0C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{044E20D7-1009-4C88-A1B6-B4630E263DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C586DB-D571-4E0C-8454-C8B6F2FA60B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8441FE-C6E7-4415-8DB0-55C129BDBDFA}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB46C81-9F11-459F-96ED-5AA54ADC317F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF247AB0-9E63-4D86-A51C-71998DAE50E8}">
   <dimension ref="B9:T19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1895,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E918A590-98E8-44F5-B283-965AE8712BE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B957939-3C2E-41B9-9781-5E29AF3F0E4C}">
   <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2937,7 +2937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA764029-DD5A-442B-962B-E7D65027B404}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E26069-F86D-4EA1-9383-3258BD83B6E2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
